--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416789\Downloads\Knowledge-Graph-AI\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F142BCB-A075-417C-823E-53C16B228628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5C7807-E98F-447E-AFA3-406F760ABB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
   <si>
     <t>Name</t>
   </si>
@@ -109,21 +109,12 @@
     <t>Immunizations</t>
   </si>
   <si>
-    <t>Patricia Hall</t>
-  </si>
-  <si>
     <t>1958-12-26</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>ajohnsm2020@gmail.com</t>
-  </si>
-  <si>
-    <t>+15551110001</t>
-  </si>
-  <si>
     <t>P1001</t>
   </si>
   <si>
@@ -187,15 +178,9 @@
     <t>Influenza|2025;Tdap|2021;Pneumococcal|2023;Shingles|2024</t>
   </si>
   <si>
-    <t>Linda Carter</t>
-  </si>
-  <si>
     <t>1955-12-27</t>
   </si>
   <si>
-    <t>+15551110002</t>
-  </si>
-  <si>
     <t>P1002</t>
   </si>
   <si>
@@ -232,15 +217,9 @@
     <t>Levothyroxine|75mcg|2012|Hypothyroidism;Calcium carbonate|600mg|2018|Bone health</t>
   </si>
   <si>
-    <t>Margaret Ross</t>
-  </si>
-  <si>
     <t>1960-12-26</t>
   </si>
   <si>
-    <t>+15551110003</t>
-  </si>
-  <si>
     <t>P1003</t>
   </si>
   <si>
@@ -263,13 +242,25 @@
   </si>
   <si>
     <t>Multivitamin|1 tab|2018|General wellness</t>
+  </si>
+  <si>
+    <t>Patric parker</t>
+  </si>
+  <si>
+    <t>Lucy venkins</t>
+  </si>
+  <si>
+    <t>Martin goswell</t>
+  </si>
+  <si>
+    <t>John.MeshachA2@cognizant.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +272,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -315,16 +314,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -626,13 +628,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="29.44140625" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="4" max="4" width="29.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.36328125" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="24.08984375" customWidth="1"/>
+    <col min="11" max="11" width="28.6328125" customWidth="1"/>
+    <col min="12" max="12" width="32" customWidth="1"/>
+    <col min="13" max="13" width="27.453125" customWidth="1"/>
+    <col min="14" max="14" width="28.90625" customWidth="1"/>
+    <col min="15" max="15" width="21.54296875" customWidth="1"/>
+    <col min="16" max="16" width="27.6328125" customWidth="1"/>
+    <col min="17" max="17" width="38.54296875" customWidth="1"/>
+    <col min="18" max="18" width="34.08984375" customWidth="1"/>
+    <col min="19" max="19" width="30.81640625" customWidth="1"/>
+    <col min="20" max="20" width="29.1796875" customWidth="1"/>
+    <col min="21" max="21" width="29.90625" customWidth="1"/>
+    <col min="22" max="22" width="38.08984375" customWidth="1"/>
+    <col min="23" max="23" width="35.1796875" customWidth="1"/>
+    <col min="24" max="24" width="27.36328125" customWidth="1"/>
+    <col min="25" max="25" width="29.7265625" customWidth="1"/>
+    <col min="26" max="26" width="28.90625" customWidth="1"/>
+    <col min="27" max="27" width="25.54296875" customWidth="1"/>
+    <col min="28" max="28" width="27.7265625" customWidth="1"/>
+    <col min="29" max="29" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,45 +745,45 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2">
+        <v>9884169146</v>
+      </c>
+      <c r="F2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>38</v>
-      </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
       </c>
       <c r="N2">
         <v>160</v>
@@ -768,87 +792,87 @@
         <v>60</v>
       </c>
       <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
         <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
       </c>
       <c r="T2">
         <v>7</v>
       </c>
       <c r="U2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" t="s">
         <v>46</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>47</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Z2" t="s">
         <v>48</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AA2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>50</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" t="s">
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3">
+        <v>9884169146</v>
+      </c>
+      <c r="F3" t="s">
         <v>53</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="I3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
         <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s">
-        <v>61</v>
       </c>
       <c r="N3">
         <v>163</v>
@@ -857,84 +881,84 @@
         <v>64</v>
       </c>
       <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
         <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>62</v>
-      </c>
-      <c r="R3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>45</v>
       </c>
       <c r="T3">
         <v>7</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
+        <v>58</v>
+      </c>
+      <c r="W3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" t="s">
         <v>63</v>
       </c>
-      <c r="W3" t="s">
+      <c r="AB3" t="s">
         <v>64</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AC3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
         <v>65</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4">
+        <v>9884169146</v>
+      </c>
+      <c r="F4" t="s">
         <v>66</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
         <v>67</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
         <v>68</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" t="s">
-        <v>75</v>
       </c>
       <c r="N4">
         <v>166</v>
@@ -943,43 +967,48 @@
         <v>68</v>
       </c>
       <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
         <v>42</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>45</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="W4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="X4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="AA4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AC4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{B423AF9C-A595-4598-82FE-3C056A6986F7}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{7522395D-C5BC-4C1D-A412-7AAFAC099DCE}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{A581AEE1-51C4-4FB3-8F62-EAABFC9D1A48}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F142BCB-A075-417C-823E-53C16B228628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C6AA91-3E86-43DA-88A4-A7CF8D035672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,9 +109,6 @@
     <t>Immunizations</t>
   </si>
   <si>
-    <t>Patricia Hall</t>
-  </si>
-  <si>
     <t>1958-12-26</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>Influenza|2025;Tdap|2021;Pneumococcal|2023;Shingles|2024</t>
   </si>
   <si>
-    <t>Linda Carter</t>
-  </si>
-  <si>
     <t>1955-12-27</t>
   </si>
   <si>
@@ -232,9 +226,6 @@
     <t>Levothyroxine|75mcg|2012|Hypothyroidism;Calcium carbonate|600mg|2018|Bone health</t>
   </si>
   <si>
-    <t>Margaret Ross</t>
-  </si>
-  <si>
     <t>1960-12-26</t>
   </si>
   <si>
@@ -263,6 +254,15 @@
   </si>
   <si>
     <t>Multivitamin|1 tab|2018|General wellness</t>
+  </si>
+  <si>
+    <t>lucy</t>
+  </si>
+  <si>
+    <t>hencika</t>
+  </si>
+  <si>
+    <t>kennyley</t>
   </si>
 </sst>
 </file>
@@ -628,6 +628,7 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="76.88671875" customWidth="1"/>
     <col min="4" max="4" width="29.44140625" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
@@ -723,43 +724,43 @@
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>38</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>40</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
       </c>
       <c r="N2">
         <v>160</v>
@@ -768,87 +769,87 @@
         <v>60</v>
       </c>
       <c r="P2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
       </c>
       <c r="T2">
         <v>7</v>
       </c>
       <c r="U2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" t="s">
         <v>46</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>47</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>48</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>50</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>52</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>53</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
         <v>57</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>58</v>
       </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
         <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s">
-        <v>61</v>
       </c>
       <c r="N3">
         <v>163</v>
@@ -857,84 +858,84 @@
         <v>64</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
         <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>45</v>
       </c>
       <c r="T3">
         <v>7</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V3" t="s">
+        <v>61</v>
+      </c>
+      <c r="W3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" t="s">
         <v>63</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>64</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>65</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>66</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>67</v>
       </c>
-      <c r="AA3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>69</v>
-      </c>
       <c r="AC3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" t="s">
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
         <v>71</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
         <v>72</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" t="s">
-        <v>75</v>
       </c>
       <c r="N4">
         <v>166</v>
@@ -943,40 +944,40 @@
         <v>68</v>
       </c>
       <c r="P4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>43</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>45</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" t="s">
+        <v>74</v>
+      </c>
+      <c r="X4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="s">
         <v>76</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AB4" t="s">
         <v>77</v>
       </c>
-      <c r="X4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>80</v>
-      </c>
       <c r="AC4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C6AA91-3E86-43DA-88A4-A7CF8D035672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485A24A8-E3D2-4A02-8669-90D87D266F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,13 +256,13 @@
     <t>Multivitamin|1 tab|2018|General wellness</t>
   </si>
   <si>
-    <t>lucy</t>
-  </si>
-  <si>
-    <t>hencika</t>
-  </si>
-  <si>
-    <t>kennyley</t>
+    <t>heny</t>
+  </si>
+  <si>
+    <t>ketty</t>
+  </si>
+  <si>
+    <t>hemakitty</t>
   </si>
 </sst>
 </file>

--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485A24A8-E3D2-4A02-8669-90D87D266F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A8A4C-C64B-4A30-B96D-F4D8DFA95AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -256,13 +256,13 @@
     <t>Multivitamin|1 tab|2018|General wellness</t>
   </si>
   <si>
-    <t>heny</t>
-  </si>
-  <si>
-    <t>ketty</t>
-  </si>
-  <si>
-    <t>hemakitty</t>
+    <t>tenny</t>
+  </si>
+  <si>
+    <t>patricy</t>
+  </si>
+  <si>
+    <t>hency</t>
   </si>
 </sst>
 </file>

--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A8A4C-C64B-4A30-B96D-F4D8DFA95AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4185690-9DB8-4176-A39F-F51474CF5669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -256,13 +256,13 @@
     <t>Multivitamin|1 tab|2018|General wellness</t>
   </si>
   <si>
-    <t>tenny</t>
-  </si>
-  <si>
-    <t>patricy</t>
-  </si>
-  <si>
-    <t>hency</t>
+    <t>Rekisha</t>
+  </si>
+  <si>
+    <t>henci</t>
+  </si>
+  <si>
+    <t>crrety</t>
   </si>
 </sst>
 </file>

--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4185690-9DB8-4176-A39F-F51474CF5669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F0AAB-E634-4B49-B8E7-F25280D1037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,13 +256,13 @@
     <t>Multivitamin|1 tab|2018|General wellness</t>
   </si>
   <si>
-    <t>Rekisha</t>
-  </si>
-  <si>
-    <t>henci</t>
-  </si>
-  <si>
-    <t>crrety</t>
+    <t>catlin</t>
+  </si>
+  <si>
+    <t>hathi</t>
+  </si>
+  <si>
+    <t>pretty</t>
   </si>
 </sst>
 </file>

--- a/bulk_upload_BCS_only_test.xlsx
+++ b/bulk_upload_BCS_only_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F0AAB-E634-4B49-B8E7-F25280D1037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AE6AA0-1B5A-4080-B916-EA03A1712E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,13 +256,13 @@
     <t>Multivitamin|1 tab|2018|General wellness</t>
   </si>
   <si>
-    <t>catlin</t>
-  </si>
-  <si>
-    <t>hathi</t>
-  </si>
-  <si>
-    <t>pretty</t>
+    <t>caty</t>
+  </si>
+  <si>
+    <t>hotkiny</t>
+  </si>
+  <si>
+    <t>printklin</t>
   </si>
 </sst>
 </file>
